--- a/artfynd/A 13237-2023 artfynd.xlsx
+++ b/artfynd/A 13237-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13237-2023 artfynd.xlsx
+++ b/artfynd/A 13237-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1619901</v>
+        <v>67725234</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,19 +704,25 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>300 M VNV FÄRJSTADEN (10I7c06), Upl</t>
+          <t>Färjestaden, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>656935.9516979057</v>
+        <v>656786</v>
       </c>
       <c r="R2" t="n">
-        <v>6585461.771711471</v>
+        <v>6585465</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +746,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1998-03-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1998-03-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-16</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>100872061 / PHE PINI / Enstaka-sparsam (1)  / OBJ.AREA:6,1 ha</t>
+          <t>Flera fruktkroppar växande på tallstam</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,75 +765,87 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Woody plant</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>David Åhlén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>David Åhlén, daniela guasconi</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Skogsstyrelsens naturvärdesobjekt</t>
+          <t>LONA-projekt Markanvändningsöversikt Ekerö kommun</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4977200</v>
+        <v>67725248</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>300 M VNV FÄRJSTADEN (10I7c06), Upl</t>
+          <t>Färjestaden, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>656935.9516979057</v>
+        <v>656882</v>
       </c>
       <c r="R3" t="n">
-        <v>6585461.771711471</v>
+        <v>6585482</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,27 +869,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1998-03-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1998-03-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-16</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>100872061 / HEPA NOB / Enstaka-sparsam (1)  / OBJ.AREA:6,1 ha</t>
+          <t>Fruktkropp växande på tallstam</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,37 +888,43 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Woody plant</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>David Åhlén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>David Åhlén, daniela guasconi</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Skogsstyrelsens naturvärdesobjekt</t>
+          <t>LONA-projekt Markanvändningsöversikt Ekerö kommun</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>67725248</v>
+        <v>67725265</v>
       </c>
       <c r="B4" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -963,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>656881.9669087592</v>
+        <v>657039</v>
       </c>
       <c r="R4" t="n">
-        <v>6585481.976062094</v>
+        <v>6585469</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,24 +995,14 @@
           <t>2017-08-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-08-16</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Fruktkropp växande på tallstam</t>
+          <t>Flera fruktkroppar växande på grov tall, 2.27m i omkr.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1055,56 +1044,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>67725234</v>
+        <v>67724289</v>
       </c>
       <c r="B5" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>102306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Färjestaden, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>656785.5898451819</v>
+        <v>656839</v>
       </c>
       <c r="R5" t="n">
-        <v>6585464.713498709</v>
+        <v>6585509</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1134,24 +1121,14 @@
           <t>2017-08-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-08-16</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar växande på tallstam</t>
+          <t>Gnagspår i barken på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,18 +1137,17 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Vedartad växt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Woody plant</t>
+          <t>Bark on living woody plant</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1193,15 +1169,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>67724289</v>
+        <v>67724324</v>
       </c>
       <c r="B6" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,10 +1213,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>656838.9521214096</v>
+        <v>656886</v>
       </c>
       <c r="R6" t="n">
-        <v>6585508.757694784</v>
+        <v>6585429</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1275,24 +1246,14 @@
           <t>2017-08-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2017-08-16</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gnagspår i barken på gran</t>
+          <t>Gnagspår i bark på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1336,12 +1297,7 @@
         <v>67724381</v>
       </c>
       <c r="B7" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,10 +1338,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>656945.5388153972</v>
+        <v>656946</v>
       </c>
       <c r="R7" t="n">
-        <v>6585366.264379593</v>
+        <v>6585366</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1415,19 +1371,9 @@
           <t>2017-08-16</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2017-08-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1462,7 +1408,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Åhlén, daniela guasconi</t>
+          <t>daniela guasconi, David Åhlén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1473,15 +1419,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>67724324</v>
+        <v>100190666</v>
       </c>
       <c r="B8" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,43 +1430,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102306</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Färjestaden, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>656886.2270388994</v>
+        <v>656945</v>
       </c>
       <c r="R8" t="n">
-        <v>6585428.589355653</v>
+        <v>6585398</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1552,27 +1496,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2017-08-16</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2017-08-16</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gnagspår i bark på gran</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1581,35 +1510,27 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant</t>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>mossig granskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>David Åhlén</t>
+          <t>Patrik Engström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>David Åhlén, daniela guasconi</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>LONA-projekt Markanvändningsöversikt Ekerö kommun</t>
-        </is>
-      </c>
+          <t>Patrik Engström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
